--- a/output/pdf_financials_xlsx/WOGC.xlsx
+++ b/output/pdf_financials_xlsx/WOGC.xlsx
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.00012</v>
       </c>
     </row>
     <row r="35">
@@ -916,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.00012</v>
       </c>
     </row>
     <row r="37">
@@ -1072,7 +1072,7 @@
         <v>0.144136</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.02063</v>
+        <v>0.02051</v>
       </c>
     </row>
     <row r="49">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/WOGC.xlsx
+++ b/output/pdf_financials_xlsx/WOGC.xlsx
@@ -690,11 +690,15 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>-0.467666</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>0.614959</v>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -704,10 +708,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.321195</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>0.611541</v>
       </c>
     </row>
     <row r="22">
@@ -2892,11 +2896,7 @@
           <t>Net income (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" s="5" t="n">
         <v>-0.146471</v>
       </c>
@@ -3770,7 +3770,11 @@
           <t>Operating income (loss) from discontinued operations 4</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>-0.321195</v>
       </c>
